--- a/data/tags/אלבומים חדשים/sites/yosmusic/2026-02-week03/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/2026-02-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דודו טסה – אי</v>
+        <v>שלומי שבן חי בגימל בהיכל התרבות</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-20</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%93%d7%95-%d7%98%d7%a1%d7%94-%d7%90%d7%99/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%9e%d7%99-%d7%a9%d7%91%d7%9f-%d7%97%d7%99-%d7%91%d7%92%d7%99%d7%9e%d7%9c-%d7%91%d7%94%d7%99%d7%9b%d7%9c-%d7%94%d7%aa%d7%a8%d7%91%d7%95%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מי מוציא היום אלבום של 18 שירים? התשובה: דודו טסה. הוא עזב את הכאוס המקומי, יצא לאי ביוון עם עלמה זוהר ויונתן דסקל, והנה התוצאה. שווה היה להתנתק. הנה מה שהאי הוליד. שווה מאוד להקשיב. האלבום נפתח ב"עמנואל" – לא</v>
+        <v>יש סיבה לחזור להיכל התרבות הריק מאדם למפגשי הקורונה של שלומי שבן.  האלבום "חי בגימל בהיכל התרבות" של שלומי שבן שנולד בתקופת הסגרים בקורונה, הוא לא עוד פרויקט קאברים – הוא תיעוד של מצב תרבותי חריג: אין קהל, אין להקה,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דודו טסה – אי</v>
+        <v>שלומי שבן חי בגימל בהיכל התרבות</v>
       </c>
     </row>
   </sheetData>
